--- a/MultiCellBMSConfig/NMC/Experiment_2_NMC_Configuration.xlsx
+++ b/MultiCellBMSConfig/NMC/Experiment_2_NMC_Configuration.xlsx
@@ -461,6 +461,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -572,7 +573,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Variable-Length CAN Mode: Set parser_type = 'waveshare_can' or 'variable_length' (Header 0xAA, DLC, CAN ID, payload, footer 0x55).</t>
+          <t xml:space="preserve">   - Variable-Length CAN Mode: Set parser_type = 'waveshare_can_variable_length' (Variable-Length CAN) (Header 0xAA, DLC, CAN ID, payload, footer 0x55).</t>
         </is>
       </c>
     </row>
@@ -590,6 +591,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -938,7 +940,6 @@
           <t>header_to_payload</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>none</t>
@@ -962,7 +963,7 @@
   </sheetData>
   <dataValidations count="13">
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"framed,waveshare_can,waveshare_can_20_bytes"</formula1>
+      <formula1>"framed,waveshare_can_variable_length,waveshare_can_20_bytes"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,4"</formula1>
@@ -1497,7 +1498,6 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>little</t>
@@ -1558,7 +1558,6 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>little</t>
@@ -1871,7 +1870,6 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>little</t>
@@ -2121,7 +2119,6 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>little</t>
@@ -2245,7 +2242,6 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>little</t>
@@ -2306,7 +2302,6 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>little</t>
@@ -2367,7 +2362,6 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>little</t>
@@ -2428,7 +2422,6 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>little</t>
@@ -2914,7 +2907,6 @@
           <t>V</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="b">
         <v>1</v>
       </c>
@@ -2935,7 +2927,6 @@
           <t>V</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="b">
         <v>1</v>
       </c>
@@ -2956,7 +2947,6 @@
           <t>°C</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="b">
         <v>1</v>
       </c>
